--- a/artfynd/A 58238-2024 artfynd.xlsx
+++ b/artfynd/A 58238-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116679692</v>
+        <v>116679761</v>
       </c>
       <c r="B2" t="n">
-        <v>96722</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334832</v>
+        <v>334824</v>
       </c>
       <c r="R2" t="n">
-        <v>6585612</v>
+        <v>6585615</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116679761</v>
+        <v>116679692</v>
       </c>
       <c r="B3" t="n">
-        <v>96730</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>224361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334824</v>
+        <v>334832</v>
       </c>
       <c r="R3" t="n">
-        <v>6585615</v>
+        <v>6585612</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
